--- a/data/trans_orig/IP07A20-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP07A20-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de llevarse bien con sus profesores en 2007 (tasa de respuesta: 99,0%)</t>
+          <t>Menores según la frecuencia de llevarse bien con el profesorado, percibida por el adulto en 2007 (tasa de respuesta: 99,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18984</t>
+          <t>18962</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30665</t>
+          <t>30196</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>39,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>63,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9442</t>
+          <t>8790</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18724</t>
+          <t>18720</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>46,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31110</t>
+          <t>30663</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45729</t>
+          <t>44955</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>51,12%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14061</t>
+          <t>14578</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25202</t>
+          <t>25242</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,97%</t>
+          <t>53,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15852</t>
+          <t>15846</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25501</t>
+          <t>25987</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>64,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32782</t>
+          <t>33270</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>47558</t>
+          <t>47993</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>54,58%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1344</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7005</t>
+          <t>6982</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8930</t>
+          <t>8842</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4459</t>
+          <t>4464</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13092</t>
+          <t>12875</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,64%</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5467</t>
+          <t>4686</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4708</t>
+          <t>4546</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10597</t>
+          <t>10232</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18924</t>
+          <t>18799</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>64,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9410</t>
+          <t>9579</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18483</t>
+          <t>18222</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>58,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22337</t>
+          <t>22262</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34900</t>
+          <t>34662</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>57,5%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7581</t>
+          <t>7632</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15672</t>
+          <t>16177</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>55,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9582</t>
+          <t>9748</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18580</t>
+          <t>18602</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>59,96%</t>
+          <t>60,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>20435</t>
+          <t>19705</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>32213</t>
+          <t>32647</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>54,16%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>645</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5948</t>
+          <t>6364</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>611</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5559</t>
+          <t>6366</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1648</t>
+          <t>1598</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8586</t>
+          <t>9345</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>15,5%</t>
         </is>
       </c>
     </row>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3233</t>
+          <t>3304</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3496</t>
+          <t>3381</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3486</t>
+          <t>3763</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3391</t>
+          <t>4098</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9877</t>
+          <t>9391</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19302</t>
+          <t>18916</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>57,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10284</t>
+          <t>9636</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20377</t>
+          <t>20076</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22395</t>
+          <t>22260</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37545</t>
+          <t>36603</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>41,81%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11892</t>
+          <t>11864</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21084</t>
+          <t>21566</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>65,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24912</t>
+          <t>25294</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>36334</t>
+          <t>36869</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,72%</t>
+          <t>67,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>39814</t>
+          <t>39447</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>55052</t>
+          <t>55305</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>45,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>63,18%</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>3858</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4805</t>
+          <t>4801</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>13709</t>
+          <t>14252</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>5774</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>15237</t>
+          <t>15796</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>18,04%</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3607</t>
+          <t>3576</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>3557</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3779</t>
+          <t>2915</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>3223</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>29513</t>
+          <t>28806</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>44408</t>
+          <t>43861</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>49,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28942</t>
+          <t>28477</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>43926</t>
+          <t>44290</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>47,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>62781</t>
+          <t>62832</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>83571</t>
+          <t>84210</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>46,06%</t>
+          <t>46,41%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>30641</t>
+          <t>30951</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>45720</t>
+          <t>45543</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>51,72%</t>
+          <t>51,52%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>33681</t>
+          <t>32958</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>48891</t>
+          <t>49038</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>52,7%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>67620</t>
+          <t>67659</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>89654</t>
+          <t>89608</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>49,38%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6031</t>
+          <t>6211</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15532</t>
+          <t>16111</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>6843</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>16578</t>
+          <t>16737</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>15377</t>
+          <t>14794</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>29835</t>
+          <t>28623</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>15,77%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>1228</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7127</t>
+          <t>7456</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1234</t>
+          <t>1223</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7030</t>
+          <t>7389</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3202</t>
+          <t>3355</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11554</t>
+          <t>11372</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -3235,7 +3235,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3038</t>
+          <t>3018</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4217</t>
+          <t>4695</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>598</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5910</t>
+          <t>5378</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>19051</t>
+          <t>20013</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>31323</t>
+          <t>31518</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>58,23%</t>
+          <t>58,59%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>22604</t>
+          <t>21707</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>34680</t>
+          <t>35225</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>49,45%</t>
+          <t>50,23%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>43625</t>
+          <t>45475</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>62155</t>
+          <t>63481</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>51,23%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>17875</t>
+          <t>17367</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>29057</t>
+          <t>28783</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>54,02%</t>
+          <t>53,51%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>22987</t>
+          <t>22828</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>35713</t>
+          <t>35915</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>51,21%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>44025</t>
+          <t>43594</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>62419</t>
+          <t>61218</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>49,4%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>1994</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>8985</t>
+          <t>8701</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>6875</t>
+          <t>6570</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>16557</t>
+          <t>16443</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>10353</t>
+          <t>10622</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>22390</t>
+          <t>22825</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,42%</t>
         </is>
       </c>
     </row>
@@ -3804,7 +3804,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3588</t>
+          <t>3629</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>4240</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>652</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6072</t>
+          <t>6167</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>9664</t>
+          <t>9838</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>19809</t>
+          <t>19602</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>47,64%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>6670</t>
+          <t>6736</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>15283</t>
+          <t>15761</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>18404</t>
+          <t>18588</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>32058</t>
+          <t>31876</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>41,39%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>15820</t>
+          <t>16193</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>26496</t>
+          <t>26782</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>64,39%</t>
+          <t>65,09%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>14079</t>
+          <t>13885</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>23588</t>
+          <t>23445</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>65,38%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>33451</t>
+          <t>33046</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>47960</t>
+          <t>47459</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>61,63%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1433</t>
+          <t>1877</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>8056</t>
+          <t>8584</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2369</t>
+          <t>2361</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>9154</t>
+          <t>8832</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>5083</t>
+          <t>4864</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>14357</t>
+          <t>14231</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,48%</t>
         </is>
       </c>
     </row>
@@ -4486,7 +4486,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4418</t>
+          <t>4294</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>5186</t>
+          <t>4598</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>688</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>6624</t>
+          <t>7194</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>9,34%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>115375</t>
+          <t>116590</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>143239</t>
+          <t>142808</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>39,75%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>48,69%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>103856</t>
+          <t>102819</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>130937</t>
+          <t>130862</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>228280</t>
+          <t>230010</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>268621</t>
+          <t>268411</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>43,42%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>116393</t>
+          <t>116381</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>144396</t>
+          <t>143148</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>48,81%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>140216</t>
+          <t>141212</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>168842</t>
+          <t>168712</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>262628</t>
+          <t>265473</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>305480</t>
+          <t>304081</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>49,19%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>18964</t>
+          <t>18997</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>35417</t>
+          <t>35466</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>33996</t>
+          <t>34594</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>53874</t>
+          <t>53630</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>56773</t>
+          <t>57656</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>81854</t>
+          <t>81331</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,16%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>2720</t>
+          <t>2662</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>11149</t>
+          <t>10490</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>4527</t>
+          <t>4732</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>14105</t>
+          <t>13794</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>9197</t>
+          <t>8683</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>20905</t>
+          <t>20877</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>5389</t>
+          <t>5824</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>4847</t>
+          <t>4896</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1284</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>7427</t>
+          <t>7350</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de llevarse bien con sus profesores en 2012 (tasa de respuesta: 97,91%)</t>
+          <t>Menores según la frecuencia de llevarse bien con el profesorado, percibida por el adulto en 2012 (tasa de respuesta: 97,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18374</t>
+          <t>18725</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28787</t>
+          <t>29110</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5755,12 +5755,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>47,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>73,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15071</t>
+          <t>15044</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24513</t>
+          <t>24661</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>43,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>70,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36061</t>
+          <t>37186</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51127</t>
+          <t>50445</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,73%</t>
+          <t>67,81%</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8958</t>
+          <t>8462</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19104</t>
+          <t>18672</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>47,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7927</t>
+          <t>7841</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16722</t>
+          <t>16748</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,98%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18958</t>
+          <t>18988</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>32753</t>
+          <t>31975</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>42,98%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>496</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5079</t>
+          <t>4882</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6006,7 +6006,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4694</t>
+          <t>4490</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6021,7 +6021,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1211</t>
+          <t>1245</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7395</t>
+          <t>7213</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,7%</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4864</t>
+          <t>4381</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5136</t>
+          <t>4398</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17519</t>
+          <t>17126</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26725</t>
+          <t>26575</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>49,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>76,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17714</t>
+          <t>17585</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26923</t>
+          <t>26804</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>50,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,7%</t>
+          <t>76,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>38684</t>
+          <t>38266</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51543</t>
+          <t>50841</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>54,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>72,82%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7988</t>
+          <t>8138</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17194</t>
+          <t>17587</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5071</t>
+          <t>5577</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13317</t>
+          <t>13714</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>15581</t>
+          <t>15729</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>27665</t>
+          <t>27927</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>40,0%</t>
         </is>
       </c>
     </row>
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>1245</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7719</t>
+          <t>7851</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1246</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7861</t>
+          <t>7516</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>10,77%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20406</t>
+          <t>20632</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30627</t>
+          <t>30975</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11420</t>
+          <t>10541</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>20011</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>62,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34581</t>
+          <t>34185</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>48411</t>
+          <t>48198</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>63,15%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10811</t>
+          <t>10449</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20439</t>
+          <t>20892</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9680</t>
+          <t>9315</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18281</t>
+          <t>18395</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>57,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>22586</t>
+          <t>22535</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>35852</t>
+          <t>36152</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>47,36%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>782</t>
+          <t>791</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6933</t>
+          <t>6699</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7370,7 +7370,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4375</t>
+          <t>5160</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7385,7 +7385,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1828</t>
+          <t>2141</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9686</t>
+          <t>9065</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>11,88%</t>
         </is>
       </c>
     </row>
@@ -7483,7 +7483,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3516</t>
+          <t>3509</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3327</t>
+          <t>2942</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4163</t>
+          <t>3928</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7611,7 +7611,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4158</t>
+          <t>3507</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7646,7 +7646,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>42609</t>
+          <t>42838</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>57819</t>
+          <t>58032</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>49,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>66,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>51057</t>
+          <t>51526</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>68119</t>
+          <t>67788</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>51,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>68,48%</t>
+          <t>68,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>99815</t>
+          <t>98877</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>121230</t>
+          <t>120268</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>53,57%</t>
+          <t>53,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>64,55%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>20813</t>
+          <t>20557</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>34906</t>
+          <t>35555</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>22550</t>
+          <t>22677</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>38037</t>
+          <t>37660</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>47085</t>
+          <t>47756</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>68077</t>
+          <t>68080</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,7 +7984,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3704</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12107</t>
+          <t>12651</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3592</t>
+          <t>3557</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12265</t>
+          <t>12380</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>8831</t>
+          <t>9401</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>20751</t>
+          <t>22006</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,81%</t>
         </is>
       </c>
     </row>
@@ -8130,7 +8130,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6830</t>
+          <t>6167</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8145,7 +8145,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8165,7 +8165,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5237</t>
+          <t>5864</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8180,7 +8180,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>953</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8309</t>
+          <t>8040</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8215,7 +8215,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4724</t>
+          <t>4721</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8313,7 +8313,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3924</t>
+          <t>4384</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>35250</t>
+          <t>34803</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>49232</t>
+          <t>48780</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>46,19%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>65,34%</t>
+          <t>64,74%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>32892</t>
+          <t>31915</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>45874</t>
+          <t>45643</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>46,06%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>63,91%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>71819</t>
+          <t>70741</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>91927</t>
+          <t>90931</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>48,2%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>61,96%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>20277</t>
+          <t>20178</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>34226</t>
+          <t>33482</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>44,43%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>16932</t>
+          <t>16430</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>29757</t>
+          <t>29741</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>41140</t>
+          <t>39753</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>60704</t>
+          <t>59170</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>40,32%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1972</t>
+          <t>1589</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>8860</t>
+          <t>8939</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1890</t>
+          <t>1863</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>8681</t>
+          <t>8762</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>4916</t>
+          <t>5009</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>15233</t>
+          <t>14041</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>9,57%</t>
         </is>
       </c>
     </row>
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>672</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>6676</t>
+          <t>6809</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>691</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6795</t>
+          <t>6887</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>608</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>5253</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8935,47 +8935,47 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>6,97%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>1853</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>561</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>5513</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
           <t>0,79%</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>6,96%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>1853</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>561</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>5143</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>2,6%</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>7561</t>
+          <t>7142</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>9800</t>
+          <t>10051</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>17721</t>
+          <t>17681</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>16515</t>
+          <t>16497</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>26348</t>
+          <t>26335</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>70,39%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>29463</t>
+          <t>28964</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>42593</t>
+          <t>42017</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>67,45%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>3735</t>
+          <t>3931</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>11590</t>
+          <t>11784</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>9162</t>
+          <t>9104</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>19045</t>
+          <t>18919</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>50,91%</t>
+          <t>50,57%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>15220</t>
+          <t>15534</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>27868</t>
+          <t>27494</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>44,14%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>594</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>5057</t>
+          <t>5353</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9416,7 +9416,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4354</t>
+          <t>4526</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>7680</t>
+          <t>7120</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>11,43%</t>
         </is>
       </c>
     </row>
@@ -9494,7 +9494,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4454</t>
+          <t>4913</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9564,7 +9564,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4997</t>
+          <t>5122</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9579,7 +9579,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -9642,57 +9642,57 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
+          <t>3012</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>8,05%</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
           <t>3092</t>
         </is>
       </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="O38" s="2" t="inlineStr">
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>8,26%</t>
-        </is>
-      </c>
-      <c r="Q38" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R38" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="S38" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T38" s="2" t="inlineStr">
-        <is>
-          <t>3264</t>
-        </is>
-      </c>
-      <c r="U38" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="V38" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>164979</t>
+          <t>166696</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>192996</t>
+          <t>194930</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>54,54%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>63,77%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>164155</t>
+          <t>164991</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>192857</t>
+          <t>191057</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>53,18%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>62,16%</t>
+          <t>61,58%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>339756</t>
+          <t>338441</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>379330</t>
+          <t>378399</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>61,44%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>88907</t>
+          <t>89643</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>116563</t>
+          <t>116119</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>89402</t>
+          <t>88794</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>115548</t>
+          <t>114681</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>186388</t>
+          <t>185394</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>223700</t>
+          <t>224481</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,45%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>12262</t>
+          <t>12249</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>26255</t>
+          <t>26975</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10078,7 +10078,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>13367</t>
+          <t>13599</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>27257</t>
+          <t>27861</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>29059</t>
+          <t>28438</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>48599</t>
+          <t>50027</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,12%</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>774</t>
+          <t>1045</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>7758</t>
+          <t>8191</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>3367</t>
+          <t>3275</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>11854</t>
+          <t>12382</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>5329</t>
+          <t>4993</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>16868</t>
+          <t>16033</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>607</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>5213</t>
+          <t>5336</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1422</t>
+          <t>1362</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>8181</t>
+          <t>8614</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>2984</t>
+          <t>2596</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>10726</t>
+          <t>10665</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10553,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de llevarse bien con sus profesores en 2016 (tasa de respuesta: 98,52%)</t>
+          <t>Menores según la frecuencia de llevarse bien con el profesorado, percibida por el adulto en 2016 (tasa de respuesta: 98,52%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17782</t>
+          <t>17743</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26549</t>
+          <t>26838</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10783,12 +10783,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18904</t>
+          <t>18917</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29177</t>
+          <t>29083</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10798,12 +10798,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>49,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>39046</t>
+          <t>39995</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>52953</t>
+          <t>53105</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10833,12 +10833,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,56%</t>
+          <t>54,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>72,63%</t>
+          <t>72,84%</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6339</t>
+          <t>6167</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14998</t>
+          <t>15607</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,33%</t>
+          <t>45,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8623</t>
+          <t>8523</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18928</t>
+          <t>18401</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>48,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17369</t>
+          <t>17969</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>30599</t>
+          <t>31138</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>42,71%</t>
         </is>
       </c>
     </row>
@@ -10979,7 +10979,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4026</t>
+          <t>4382</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10994,7 +10994,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11014,7 +11014,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3903</t>
+          <t>3474</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11029,7 +11029,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>615</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5409</t>
+          <t>5777</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,92%</t>
         </is>
       </c>
     </row>
@@ -11092,7 +11092,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3296</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11107,7 +11107,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11162,7 +11162,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>3249</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17733</t>
+          <t>17757</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30040</t>
+          <t>29573</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11445,12 +11445,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>57,25%</t>
+          <t>56,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21941</t>
+          <t>22337</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33485</t>
+          <t>33188</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>46,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>69,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>43250</t>
+          <t>43270</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>60368</t>
+          <t>60436</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11515,12 +11515,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,24%</t>
+          <t>60,31%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18368</t>
+          <t>18776</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30893</t>
+          <t>30519</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>58,87%</t>
+          <t>58,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9346</t>
+          <t>9536</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20312</t>
+          <t>19476</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>30640</t>
+          <t>29962</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>48026</t>
+          <t>47075</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>46,98%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1883</t>
+          <t>1925</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8537</t>
+          <t>8282</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2111</t>
+          <t>2152</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9099</t>
+          <t>8987</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4997</t>
+          <t>4851</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>14372</t>
+          <t>14224</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,19%</t>
         </is>
       </c>
     </row>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3788</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4178</t>
+          <t>4460</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -12112,12 +12112,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9612</t>
+          <t>9547</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18174</t>
+          <t>18424</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12127,12 +12127,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>64,67%</t>
+          <t>65,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12147,12 +12147,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15503</t>
+          <t>15344</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26458</t>
+          <t>25969</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12162,12 +12162,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>63,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28407</t>
+          <t>28195</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>42087</t>
+          <t>42185</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12197,12 +12197,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>60,9%</t>
+          <t>61,04%</t>
         </is>
       </c>
     </row>
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5667</t>
+          <t>5854</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13640</t>
+          <t>14399</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,54%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11838</t>
+          <t>11962</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22794</t>
+          <t>22672</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>55,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>19564</t>
+          <t>20111</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>33378</t>
+          <t>33567</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>48,57%</t>
         </is>
       </c>
     </row>
@@ -12338,12 +12338,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>728</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6917</t>
+          <t>6968</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12378,7 +12378,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5298</t>
+          <t>4641</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>1655</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9105</t>
+          <t>9319</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,49%</t>
         </is>
       </c>
     </row>
@@ -12456,7 +12456,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3580</t>
+          <t>3320</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12471,7 +12471,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12491,7 +12491,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3723</t>
+          <t>3493</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12506,7 +12506,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12526,7 +12526,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5157</t>
+          <t>5257</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12541,7 +12541,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,61%</t>
         </is>
       </c>
     </row>
@@ -12569,7 +12569,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4796</t>
+          <t>5432</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12584,7 +12584,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12604,7 +12604,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3678</t>
+          <t>3388</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12619,7 +12619,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12639,7 +12639,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6393</t>
+          <t>6396</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12654,7 +12654,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,26%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>51365</t>
+          <t>51911</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>69011</t>
+          <t>69368</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>45,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>60,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>46351</t>
+          <t>46501</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>63720</t>
+          <t>63872</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>44,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>61,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>102994</t>
+          <t>102129</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>127397</t>
+          <t>126858</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>47,1%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>58,02%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>34395</t>
+          <t>33600</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>51810</t>
+          <t>51441</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>29877</t>
+          <t>29626</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>47645</t>
+          <t>46356</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>46,02%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>69359</t>
+          <t>69908</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>92516</t>
+          <t>93359</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,7%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6800</t>
+          <t>7033</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>17632</t>
+          <t>17505</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4882</t>
+          <t>4949</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>15200</t>
+          <t>14765</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>13813</t>
+          <t>14623</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>28235</t>
+          <t>29425</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,46%</t>
         </is>
       </c>
     </row>
@@ -13251,7 +13251,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3159</t>
+          <t>2778</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13286,7 +13286,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4782</t>
+          <t>4167</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13301,7 +13301,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13316,12 +13316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>626</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5411</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13336,7 +13336,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -13476,12 +13476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>31735</t>
+          <t>31972</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>46244</t>
+          <t>45983</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13511,12 +13511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>27416</t>
+          <t>27292</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>42024</t>
+          <t>41811</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>57,95%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>63950</t>
+          <t>63285</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>84832</t>
+          <t>83595</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>56,73%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>20862</t>
+          <t>20353</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>34419</t>
+          <t>34386</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>45,73%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>23301</t>
+          <t>22784</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>36963</t>
+          <t>36298</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>46944</t>
+          <t>47282</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>65706</t>
+          <t>66742</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>45,3%</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4686</t>
+          <t>4936</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>14046</t>
+          <t>13835</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>2205</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>10258</t>
+          <t>10506</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>8730</t>
+          <t>9248</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>20596</t>
+          <t>20860</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,16%</t>
         </is>
       </c>
     </row>
@@ -13855,7 +13855,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5646</t>
+          <t>5669</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13870,7 +13870,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>647</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>5697</t>
+          <t>5784</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13900,12 +13900,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -13968,7 +13968,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3558</t>
+          <t>3607</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13983,7 +13983,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14003,7 +14003,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3984</t>
+          <t>3486</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14018,7 +14018,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -14158,12 +14158,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>13705</t>
+          <t>13610</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>23024</t>
+          <t>22534</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>71,52%</t>
+          <t>70,0%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>14625</t>
+          <t>14224</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>25018</t>
+          <t>24922</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>64,46%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>30856</t>
+          <t>30514</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>44434</t>
+          <t>44381</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>62,64%</t>
         </is>
       </c>
     </row>
@@ -14271,12 +14271,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>8288</t>
+          <t>8651</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>17601</t>
+          <t>17585</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14286,12 +14286,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>54,62%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>6238</t>
+          <t>6561</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>15698</t>
+          <t>15524</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14321,12 +14321,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>16925</t>
+          <t>17493</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>30332</t>
+          <t>30259</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>42,71%</t>
         </is>
       </c>
     </row>
@@ -14389,7 +14389,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4230</t>
+          <t>4172</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14404,7 +14404,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2973</t>
+          <t>2931</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>10660</t>
+          <t>10942</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14434,12 +14434,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>3686</t>
+          <t>3737</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>12699</t>
+          <t>12991</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,34%</t>
         </is>
       </c>
     </row>
@@ -14537,7 +14537,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>4620</t>
+          <t>5136</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14552,7 +14552,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14572,7 +14572,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4612</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14587,7 +14587,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,6%</t>
         </is>
       </c>
     </row>
@@ -14650,7 +14650,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3468</t>
+          <t>3461</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3488</t>
+          <t>3455</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14700,7 +14700,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>162751</t>
+          <t>163309</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>193003</t>
+          <t>192172</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>48,36%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>165700</t>
+          <t>167590</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>197656</t>
+          <t>197423</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>48,54%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>57,83%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>338886</t>
+          <t>339284</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>385581</t>
+          <t>382197</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,12 +14925,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>49,96%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>56,28%</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>112406</t>
+          <t>112211</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>141908</t>
+          <t>141300</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>41,84%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>109670</t>
+          <t>108952</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>140013</t>
+          <t>138681</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>40,63%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>227488</t>
+          <t>228945</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>270796</t>
+          <t>271204</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>39,94%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>22248</t>
+          <t>22412</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>39322</t>
+          <t>39350</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>19926</t>
+          <t>19762</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>37231</t>
+          <t>36545</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>46303</t>
+          <t>44249</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>69859</t>
+          <t>68396</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,07%</t>
         </is>
       </c>
     </row>
@@ -15184,7 +15184,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>4873</t>
+          <t>4382</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15199,7 +15199,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>2116</t>
+          <t>2190</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>10086</t>
+          <t>9961</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15229,12 +15229,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>3152</t>
+          <t>3377</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>12590</t>
+          <t>12856</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15264,12 +15264,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -15297,7 +15297,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>5652</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15312,7 +15312,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15327,12 +15327,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1359</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>7640</t>
+          <t>7709</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15347,7 +15347,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>2106</t>
+          <t>2060</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>9858</t>
+          <t>10027</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15377,12 +15377,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
